--- a/ig/mc-changes/StructureDefinition-as-practitioner.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6787" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6792" uniqueCount="709">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T12:40:41+00:00</t>
+    <t>2023-05-09T14:30:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,10 +439,13 @@
 </t>
   </si>
   <si>
-    <t>[DR] : nationalite</t>
-  </si>
-  <si>
-    <t>Nationalité de la personne</t>
+    <t>[Donnée restreinte] : Nationalité de la personne.</t>
+  </si>
+  <si>
+    <t>Nationalité du professionnel</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : nationalite</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-practitioner-authorization</t>
@@ -455,10 +458,13 @@
 </t>
   </si>
   <si>
-    <t>[DR] : autorisationExercice</t>
-  </si>
-  <si>
-    <t>L'autorisation d'exercice pour les personnes diposant de diplômes étrangers non reconnus en France</t>
+    <t>L'autorisation d'exercice pour les personnes diposant de diplômes étrangers non reconnus en France.</t>
+  </si>
+  <si>
+    <t>Il s'agit d'une autorisation délivrée par le Ministère de la Santé ou par l'Ordre au professionnel pour accès à l'exercice de la profession.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : autorisationExercice</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-practitioner-birth-place</t>
@@ -471,10 +477,13 @@
 </t>
   </si>
   <si>
-    <t>[DR] : lieuNaissance</t>
-  </si>
-  <si>
-    <t>Code officiel géographique (COG) de la commune (France) ou du pays</t>
+    <t>[Donnée restreinte] : Code officiel géographique (COG) de la commune (France) ou du pays</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du lieu de naissance du professionnel (Practitioner).</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : lieuNaissance</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-practitioner-deceased-date-time</t>
@@ -487,10 +496,13 @@
 </t>
   </si>
   <si>
-    <t>[DR] : dateDeces</t>
-  </si>
-  <si>
-    <t>Date de décès de la personne</t>
+    <t>[Donnée restreinte] : Date de décès de la personne.</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la date de décès du professionnel (Date of death of the practitioner if applicable).</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : dateDeces</t>
   </si>
   <si>
     <t>Practitioner.modifierExtension</t>
@@ -584,13 +596,14 @@
 </t>
   </si>
   <si>
-    <t>typeIdNat_PP</t>
+    <t>Type d’identifiant national de la personne physique.</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>Les code ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les code 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+    <t>Synonymes MOS : typeIdNat_PP,
+Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
@@ -754,7 +767,7 @@
     <t>Practitioner.identifier.system</t>
   </si>
   <si>
-    <t>le système de l'identifiant dépend de la source d'où provient l'identifiant</t>
+    <t>le système de l'identifiant dépend de la source d'où provient l'identifiant.</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a OID that describes a set values that are unique.
@@ -778,13 +791,13 @@
     <t>Practitioner.identifier.value</t>
   </si>
   <si>
-    <t>idPP</t>
+    <t>Identifiant national de la personne physique.</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>la valeur de l'identifiant du PS</t>
+    <t>Synonyme MOS : idPP</t>
   </si>
   <si>
     <t>123456</t>
@@ -843,7 +856,7 @@
     <t>Practitioner.active</t>
   </si>
   <si>
-    <t>isActive</t>
+    <t>Le professionnel est-il actif? active | inactive</t>
   </si>
   <si>
     <t>Whether this practitioner's record is in active use.</t>
@@ -948,7 +961,7 @@
 </t>
   </si>
   <si>
-    <t>[DR] : nomFamille/nomUsage</t>
+    <t>[Donnée restreinte] : Le nom de famille (également nommé nom de naissance) ou le nom d'usage de la personne.</t>
   </si>
   <si>
     <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
@@ -967,7 +980,7 @@
 middle name</t>
   </si>
   <si>
-    <t>[DR] : prenom/prenomUsuel</t>
+    <t>[Donnée restreinte] : Prénom(s) déclarés à sa naissance de la personne.</t>
   </si>
   <si>
     <t>Given name.</t>
@@ -982,10 +995,13 @@
     <t>Practitioner.name.prefix</t>
   </si>
   <si>
-    <t>civilite</t>
+    <t>Civilité de la personne physique.</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : civilite</t>
   </si>
   <si>
     <t>Civilités des personnes physiques du RASS</t>
@@ -1041,13 +1057,13 @@
 </t>
   </si>
   <si>
-    <t>[DR] : telecommunication</t>
+    <t>Différentes instances pour les téléphones, la télécopie et l’adresse mail.</t>
   </si>
   <si>
     <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
   </si>
   <si>
-    <t>Différentes instances pour les téléphones, la télécopie et l’adresse mail</t>
+    <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently and to help with identification.  These typically will have home numbers, or mobile numbers that are not role specific.</t>
   </si>
   <si>
     <t>Need to know how to reach a practitioner independent to any roles the practitioner may have.</t>
@@ -1194,13 +1210,10 @@
 </t>
   </si>
   <si>
-    <t>boiteLettreMSS</t>
-  </si>
-  <si>
-    <t>Les BALs MSS de type PER rattachées seulement à l'identifiant du professionnel de Santé</t>
-  </si>
-  <si>
-    <t>Person may have multiple ways to be contacted with different uses or applicable periods.  May need to have options for contacting the person urgently and to help with identification.  These typically will have home numbers, or mobile numbers that are not role specific.</t>
+    <t>Les BALs MSS de type PER rattachées seulement à l'identifiant du professionnel de Santé.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : boiteLettreMSS</t>
   </si>
   <si>
     <t>Practitioner.telecom:mailbox-mss.id</t>
@@ -1237,13 +1250,13 @@
 </t>
   </si>
   <si>
-    <t>[DR] : adresseCorrespondance</t>
+    <t>[Donnée restreinte] : Adresse(s) de correspondance permettant de contacter le professionnel.</t>
   </si>
   <si>
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
   </si>
   <si>
-    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
+    <t>Synonyme MOS : adresseCorrespondance</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
@@ -1252,10 +1265,13 @@
     <t>Practitioner.gender</t>
   </si>
   <si>
-    <t>[DR] : sexeAdministratif</t>
+    <t>[Donnée restreinte] : Sexe administratif de la personne physique, au sens de l'état civil, masculin ou féminin.</t>
   </si>
   <si>
     <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : sexeAdministratif</t>
   </si>
   <si>
     <t>Needed to address the person correctly.</t>
@@ -1271,10 +1287,13 @@
 </t>
   </si>
   <si>
-    <t>[DR] - dateNaissance</t>
+    <t>[Donnée restreinte] : Date de naissance de la personne, modifiée selon les règles du RNIV dans le cas des dates exceptionnelles.</t>
   </si>
   <si>
     <t>The date of birth for the practitioner.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : dateNaissance</t>
   </si>
   <si>
     <t>Needed for identification.</t>
@@ -1391,33 +1410,39 @@
     <t>degreeR36</t>
   </si>
   <si>
-    <t>autreDiplomeObtenu</t>
+    <t>Autre diplôme obtenu.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : tautreDiplomeObtenu</t>
+  </si>
+  <si>
+    <t>Liste des diplômes</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:degreeR36.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:degreeR36.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:degreeR36.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.system</t>
   </si>
   <si>
     <t>Autre diplôme obtenu</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding:degreeR36.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding:degreeR36.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding:degreeR36.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.system</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R36-AutreDiplomeObtenu/FHIR/TRE-R36-AutreDiplomeObtenu</t>
   </si>
   <si>
@@ -1451,10 +1476,13 @@
     <t>degreeR47</t>
   </si>
   <si>
-    <t>qualification</t>
-  </si>
-  <si>
-    <t>Qualification attribuée par une commission</t>
+    <t>Qualification attribuée par une commission.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : qualification</t>
+  </si>
+  <si>
+    <t>Liste des qualifications</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR47.id</t>
@@ -1490,10 +1518,13 @@
     <t>degreeR48</t>
   </si>
   <si>
-    <t>DiplomeEtat</t>
-  </si>
-  <si>
-    <t>Ensemble des diplômes et qualifications</t>
+    <t>Diplôme d'Etat français.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : DiplomeEtat</t>
+  </si>
+  <si>
+    <t>Liste des diplômes et qualifications</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR48.id</t>
@@ -1529,7 +1560,13 @@
     <t>degreeR49</t>
   </si>
   <si>
-    <t>DiplomeEtudeSpecialisee</t>
+    <t>Diplôme d'études spécialisées (DES).</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : DiplomeEtudeSpecialisee</t>
+  </si>
+  <si>
+    <t>Liste des DES</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR49.id</t>
@@ -1565,7 +1602,13 @@
     <t>degreeR50</t>
   </si>
   <si>
-    <t>DESC1</t>
+    <t>Diplôme d'études spécialisées complémentaires non qualifiants (DESC I).</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : DESC1</t>
+  </si>
+  <si>
+    <t>Liste des DES I</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR50.id</t>
@@ -1601,7 +1644,13 @@
     <t>degreeR51</t>
   </si>
   <si>
-    <t>DESC2</t>
+    <t>Diplôme d'études spécialisées complémentaires qualifiants (DESC II).</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : DESC2</t>
+  </si>
+  <si>
+    <t>Liste des DESC II</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR51.id</t>
@@ -1637,10 +1686,10 @@
     <t>degreeR52</t>
   </si>
   <si>
-    <t>capaciteDiplome</t>
-  </si>
-  <si>
-    <t>Diplôme de capacité de médecine</t>
+    <t>Diplôme de capacité de médecine.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : capaciteDiplome</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR52.id</t>
@@ -1676,10 +1725,10 @@
     <t>degreeR53</t>
   </si>
   <si>
-    <t>DiplomeEEE</t>
-  </si>
-  <si>
-    <t>Diplôme d'un pays de l'espace économique européen</t>
+    <t>Synonyme MOS : DiplomeEEE</t>
+  </si>
+  <si>
+    <t>Liste des diplômes EEE</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR53.id</t>
@@ -1715,10 +1764,10 @@
     <t>degreeR54</t>
   </si>
   <si>
-    <t>DiplomeUniversitaire</t>
-  </si>
-  <si>
-    <t>Diplôme universitaire ou interuniversitaire</t>
+    <t>Diplôme universitaire ou interuniversitaire.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : DiplomeUniversitaire</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR54.id</t>
@@ -1754,10 +1803,13 @@
     <t>degreeR55</t>
   </si>
   <si>
-    <t>certificatEtudeSpeciale</t>
-  </si>
-  <si>
-    <t>Certificat d'études spéciales (CES)</t>
+    <t>Certificat d'études spéciales (CES).</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : certificatEtudeSpeciale</t>
+  </si>
+  <si>
+    <t>Liste des CES</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR55.id</t>
@@ -1793,10 +1845,13 @@
     <t>degreeR56</t>
   </si>
   <si>
-    <t>attestation</t>
-  </si>
-  <si>
-    <t>Attestation de formation</t>
+    <t>Attestation de formation.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : attestation</t>
+  </si>
+  <si>
+    <t>Liste des attestations</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR56.id</t>
@@ -1832,10 +1887,13 @@
     <t>degreeR57</t>
   </si>
   <si>
-    <t>DiplomeEES</t>
-  </si>
-  <si>
-    <t>Diplôme européen d'études spécialisées</t>
+    <t>Diplôme européen d'études spécialisées.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : DiplomeEES</t>
+  </si>
+  <si>
+    <t>Liste des diplômes EES</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR57.id</t>
@@ -1871,12 +1929,12 @@
     <t>degreeR58</t>
   </si>
   <si>
-    <t>DiplomeDivers</t>
-  </si>
-  <si>
     <t>Autre type de diplôme obtenu</t>
   </si>
   <si>
+    <t>Synonyme MOS : DiplomeDivers</t>
+  </si>
+  <si>
     <t>Practitioner.qualification.code.coding:degreeR58.id</t>
   </si>
   <si>
@@ -1910,10 +1968,10 @@
     <t>degreeR226</t>
   </si>
   <si>
-    <t>diplomeDeuxiemeCycleNonQualifiant</t>
-  </si>
-  <si>
-    <t>Diplôme de deuxième cycle non qualifiant</t>
+    <t>Diplôme de deuxième cycle non qualifiant.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : diplomeDeuxiemeCycleNonQualifiant</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.coding:degreeR226.id</t>
@@ -1949,7 +2007,10 @@
     <t>degreeType</t>
   </si>
   <si>
-    <t>typeDiplome</t>
+    <t>Type de diplôme.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : typeDiplome</t>
   </si>
   <si>
     <t>Liste des types de diplôme</t>
@@ -2129,10 +2190,13 @@
 </t>
   </si>
   <si>
-    <t>langueParlee</t>
+    <t>Langue parlée.</t>
   </si>
   <si>
     <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : langueParlee</t>
   </si>
   <si>
     <t>Knowing which language a practitioner speaks can help in facilitating communication with patients.</t>
@@ -3447,7 +3511,9 @@
       <c r="M10" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="N10" s="2"/>
+      <c r="N10" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>71</v>
@@ -3513,13 +3579,13 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>71</v>
@@ -3541,15 +3607,17 @@
         <v>71</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>71</v>
@@ -3615,13 +3683,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>71</v>
@@ -3643,15 +3711,17 @@
         <v>71</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>71</v>
@@ -3717,13 +3787,13 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>71</v>
@@ -3745,15 +3815,17 @@
         <v>71</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>71</v>
@@ -3819,10 +3891,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3848,16 +3920,16 @@
         <v>123</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>71</v>
@@ -3906,7 +3978,7 @@
         <v>129</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>72</v>
@@ -3923,10 +3995,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3949,17 +4021,17 @@
         <v>79</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>71</v>
@@ -4008,7 +4080,7 @@
         <v>71</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>72</v>
@@ -4025,10 +4097,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4051,13 +4123,13 @@
         <v>71</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4108,7 +4180,7 @@
         <v>71</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>72</v>
@@ -4125,10 +4197,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4157,7 +4229,7 @@
         <v>124</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>126</v>
@@ -4210,7 +4282,7 @@
         <v>129</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>72</v>
@@ -4227,10 +4299,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4256,16 +4328,16 @@
         <v>99</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>71</v>
@@ -4290,13 +4362,13 @@
         <v>71</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>71</v>
@@ -4314,7 +4386,7 @@
         <v>71</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>72</v>
@@ -4331,10 +4403,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4357,19 +4429,19 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>71</v>
@@ -4394,13 +4466,13 @@
         <v>71</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>71</v>
@@ -4418,7 +4490,7 @@
         <v>71</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>72</v>
@@ -4435,10 +4507,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4461,13 +4533,13 @@
         <v>71</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4518,7 +4590,7 @@
         <v>71</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>72</v>
@@ -4535,10 +4607,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4567,7 +4639,7 @@
         <v>124</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>126</v>
@@ -4620,7 +4692,7 @@
         <v>129</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>72</v>
@@ -4637,10 +4709,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4663,19 +4735,19 @@
         <v>79</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>71</v>
@@ -4724,7 +4796,7 @@
         <v>71</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>72</v>
@@ -4741,10 +4813,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4767,13 +4839,13 @@
         <v>71</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4824,7 +4896,7 @@
         <v>71</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>72</v>
@@ -4841,10 +4913,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4873,7 +4945,7 @@
         <v>124</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>126</v>
@@ -4926,7 +4998,7 @@
         <v>129</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>72</v>
@@ -4943,10 +5015,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4972,16 +5044,16 @@
         <v>93</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>71</v>
@@ -4994,7 +5066,7 @@
         <v>71</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="U25" t="s" s="2">
         <v>71</v>
@@ -5030,7 +5102,7 @@
         <v>71</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>72</v>
@@ -5047,10 +5119,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5073,16 +5145,16 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5132,7 +5204,7 @@
         <v>71</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>72</v>
@@ -5149,10 +5221,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5178,16 +5250,16 @@
         <v>99</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>71</v>
@@ -5236,7 +5308,7 @@
         <v>71</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>72</v>
@@ -5253,10 +5325,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5279,19 +5351,19 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O28" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>71</v>
@@ -5340,7 +5412,7 @@
         <v>71</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>72</v>
@@ -5357,10 +5429,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5383,19 +5455,19 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>71</v>
@@ -5444,7 +5516,7 @@
         <v>71</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>72</v>
@@ -5461,10 +5533,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5487,19 +5559,19 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>71</v>
@@ -5548,7 +5620,7 @@
         <v>71</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>72</v>
@@ -5565,10 +5637,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5594,16 +5666,16 @@
         <v>93</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>71</v>
@@ -5616,7 +5688,7 @@
         <v>71</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>71</v>
@@ -5652,7 +5724,7 @@
         <v>71</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>72</v>
@@ -5669,10 +5741,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5695,16 +5767,16 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5718,7 +5790,7 @@
         <v>71</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>71</v>
@@ -5754,7 +5826,7 @@
         <v>71</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>72</v>
@@ -5771,10 +5843,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5797,16 +5869,16 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5856,7 +5928,7 @@
         <v>71</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>72</v>
@@ -5868,15 +5940,15 @@
         <v>90</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5899,16 +5971,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5958,7 +6030,7 @@
         <v>71</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>72</v>
@@ -5970,15 +6042,15 @@
         <v>90</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6001,70 +6073,70 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O35" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q35" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="R35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="P35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Q35" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="R35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>72</v>
@@ -6081,10 +6153,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6107,19 +6179,19 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>71</v>
@@ -6168,7 +6240,7 @@
         <v>71</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>72</v>
@@ -6185,10 +6257,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6211,13 +6283,13 @@
         <v>71</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6268,7 +6340,7 @@
         <v>71</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>72</v>
@@ -6285,10 +6357,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6317,7 +6389,7 @@
         <v>124</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>126</v>
@@ -6370,7 +6442,7 @@
         <v>129</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>72</v>
@@ -6387,13 +6459,13 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>122</v>
@@ -6415,13 +6487,13 @@
         <v>71</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>126</v>
@@ -6474,7 +6546,7 @@
         <v>71</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>72</v>
@@ -6491,10 +6563,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6520,16 +6592,16 @@
         <v>99</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>71</v>
@@ -6554,13 +6626,13 @@
         <v>71</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>71</v>
@@ -6578,7 +6650,7 @@
         <v>71</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>72</v>
@@ -6595,10 +6667,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6621,19 +6693,19 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>71</v>
@@ -6682,7 +6754,7 @@
         <v>71</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>72</v>
@@ -6699,14 +6771,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6725,16 +6797,16 @@
         <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6784,7 +6856,7 @@
         <v>71</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>72</v>
@@ -6801,14 +6873,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6827,16 +6899,16 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6886,7 +6958,7 @@
         <v>71</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>72</v>
@@ -6903,10 +6975,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6929,16 +7001,16 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>215</v>
+        <v>315</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6964,13 +7036,13 @@
         <v>71</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>71</v>
@@ -6988,7 +7060,7 @@
         <v>71</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>72</v>
@@ -7005,10 +7077,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7031,16 +7103,16 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7066,13 +7138,13 @@
         <v>71</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>71</v>
@@ -7090,7 +7162,7 @@
         <v>71</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>72</v>
@@ -7107,10 +7179,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7133,19 +7205,19 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>71</v>
@@ -7194,7 +7266,7 @@
         <v>71</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>72</v>
@@ -7206,15 +7278,15 @@
         <v>90</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7237,19 +7309,19 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>71</v>
@@ -7286,7 +7358,7 @@
         <v>71</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -7296,7 +7368,7 @@
         <v>129</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>72</v>
@@ -7308,15 +7380,15 @@
         <v>90</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7339,13 +7411,13 @@
         <v>71</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7396,7 +7468,7 @@
         <v>71</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>72</v>
@@ -7413,10 +7485,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7445,7 +7517,7 @@
         <v>124</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>126</v>
@@ -7498,7 +7570,7 @@
         <v>129</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>72</v>
@@ -7515,13 +7587,13 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>122</v>
@@ -7543,13 +7615,13 @@
         <v>71</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>126</v>
@@ -7602,7 +7674,7 @@
         <v>71</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>72</v>
@@ -7619,10 +7691,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7648,13 +7720,13 @@
         <v>99</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7668,7 +7740,7 @@
         <v>71</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>71</v>
@@ -7680,13 +7752,13 @@
         <v>71</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>71</v>
@@ -7704,7 +7776,7 @@
         <v>71</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>72</v>
@@ -7713,7 +7785,7 @@
         <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>91</v>
@@ -7721,10 +7793,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7747,19 +7819,19 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>71</v>
@@ -7808,7 +7880,7 @@
         <v>71</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>72</v>
@@ -7825,10 +7897,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7854,16 +7926,16 @@
         <v>99</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>71</v>
@@ -7888,13 +7960,13 @@
         <v>71</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>71</v>
@@ -7912,7 +7984,7 @@
         <v>71</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>72</v>
@@ -7929,10 +8001,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7955,16 +8027,16 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8014,7 +8086,7 @@
         <v>71</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>72</v>
@@ -8031,10 +8103,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8057,16 +8129,16 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8116,7 +8188,7 @@
         <v>71</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>72</v>
@@ -8128,18 +8200,18 @@
         <v>90</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>71</v>
@@ -8161,19 +8233,19 @@
         <v>71</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>378</v>
+        <v>334</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>71</v>
@@ -8222,7 +8294,7 @@
         <v>71</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>72</v>
@@ -8234,15 +8306,15 @@
         <v>90</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8265,13 +8337,13 @@
         <v>71</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8322,7 +8394,7 @@
         <v>71</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>72</v>
@@ -8339,10 +8411,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8371,7 +8443,7 @@
         <v>124</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>126</v>
@@ -8424,7 +8496,7 @@
         <v>129</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>72</v>
@@ -8441,13 +8513,13 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>122</v>
@@ -8469,13 +8541,13 @@
         <v>71</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>126</v>
@@ -8528,7 +8600,7 @@
         <v>71</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>72</v>
@@ -8545,10 +8617,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8574,13 +8646,13 @@
         <v>99</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8594,7 +8666,7 @@
         <v>71</v>
       </c>
       <c r="T60" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="U60" t="s" s="2">
         <v>71</v>
@@ -8606,13 +8678,13 @@
         <v>71</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>71</v>
@@ -8630,7 +8702,7 @@
         <v>71</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>72</v>
@@ -8639,7 +8711,7 @@
         <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>91</v>
@@ -8647,10 +8719,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8673,19 +8745,19 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>71</v>
@@ -8734,7 +8806,7 @@
         <v>71</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>72</v>
@@ -8751,10 +8823,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8780,16 +8852,16 @@
         <v>99</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>71</v>
@@ -8814,13 +8886,13 @@
         <v>71</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>71</v>
@@ -8838,7 +8910,7 @@
         <v>71</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>72</v>
@@ -8855,10 +8927,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8881,16 +8953,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8940,7 +9012,7 @@
         <v>71</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>72</v>
@@ -8957,10 +9029,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8983,16 +9055,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9042,7 +9114,7 @@
         <v>71</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>72</v>
@@ -9054,15 +9126,15 @@
         <v>90</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9085,19 +9157,19 @@
         <v>71</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>71</v>
@@ -9146,7 +9218,7 @@
         <v>71</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>72</v>
@@ -9163,10 +9235,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9192,16 +9264,16 @@
         <v>99</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>215</v>
+        <v>402</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>71</v>
@@ -9226,29 +9298,29 @@
         <v>71</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>72</v>
@@ -9265,10 +9337,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9291,17 +9363,19 @@
         <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="O67" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>71</v>
@@ -9350,7 +9424,7 @@
         <v>71</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>72</v>
@@ -9367,10 +9441,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9393,19 +9467,19 @@
         <v>71</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>71</v>
@@ -9454,7 +9528,7 @@
         <v>71</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>72</v>
@@ -9466,15 +9540,15 @@
         <v>90</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9497,13 +9571,13 @@
         <v>71</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9554,7 +9628,7 @@
         <v>71</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>72</v>
@@ -9571,10 +9645,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9597,13 +9671,13 @@
         <v>71</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9654,7 +9728,7 @@
         <v>71</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>72</v>
@@ -9671,10 +9745,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9703,7 +9777,7 @@
         <v>124</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>126</v>
@@ -9756,7 +9830,7 @@
         <v>129</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>72</v>
@@ -9773,14 +9847,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9802,16 +9876,16 @@
         <v>123</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>126</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>71</v>
@@ -9860,7 +9934,7 @@
         <v>71</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>72</v>
@@ -9877,10 +9951,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9903,17 +9977,17 @@
         <v>71</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>71</v>
@@ -9962,7 +10036,7 @@
         <v>71</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>72</v>
@@ -9979,10 +10053,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10005,16 +10079,16 @@
         <v>71</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10040,31 +10114,31 @@
         <v>71</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="Z74" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10081,10 +10155,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10107,13 +10181,13 @@
         <v>71</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10164,7 +10238,7 @@
         <v>71</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>72</v>
@@ -10181,10 +10255,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10213,7 +10287,7 @@
         <v>124</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>126</v>
@@ -10266,7 +10340,7 @@
         <v>129</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>72</v>
@@ -10283,10 +10357,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10309,19 +10383,19 @@
         <v>79</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>71</v>
@@ -10358,7 +10432,7 @@
         <v>71</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="AC77" s="2"/>
       <c r="AD77" t="s" s="2">
@@ -10368,7 +10442,7 @@
         <v>129</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>72</v>
@@ -10385,13 +10459,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>71</v>
@@ -10413,19 +10487,19 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>195</v>
+        <v>447</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>71</v>
@@ -10450,13 +10524,13 @@
         <v>71</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>71</v>
@@ -10474,7 +10548,7 @@
         <v>71</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>72</v>
@@ -10491,10 +10565,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10517,13 +10591,13 @@
         <v>71</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10574,7 +10648,7 @@
         <v>71</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>72</v>
@@ -10591,10 +10665,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10623,7 +10697,7 @@
         <v>124</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>126</v>
@@ -10676,7 +10750,7 @@
         <v>129</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>72</v>
@@ -10693,10 +10767,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10722,23 +10796,23 @@
         <v>93</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>71</v>
@@ -10780,7 +10854,7 @@
         <v>71</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>72</v>
@@ -10797,10 +10871,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10823,16 +10897,16 @@
         <v>79</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -10882,7 +10956,7 @@
         <v>71</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>72</v>
@@ -10899,10 +10973,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10928,16 +11002,16 @@
         <v>99</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>71</v>
@@ -10986,7 +11060,7 @@
         <v>71</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>72</v>
@@ -11003,10 +11077,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11029,19 +11103,19 @@
         <v>79</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M84" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>71</v>
@@ -11090,7 +11164,7 @@
         <v>71</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>72</v>
@@ -11107,10 +11181,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11133,19 +11207,19 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>71</v>
@@ -11194,7 +11268,7 @@
         <v>71</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>72</v>
@@ -11211,13 +11285,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>71</v>
@@ -11239,19 +11313,19 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>195</v>
+        <v>469</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>71</v>
@@ -11276,13 +11350,13 @@
         <v>71</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>71</v>
@@ -11300,7 +11374,7 @@
         <v>71</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>72</v>
@@ -11317,10 +11391,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11343,13 +11417,13 @@
         <v>71</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11400,7 +11474,7 @@
         <v>71</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>72</v>
@@ -11417,10 +11491,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11449,7 +11523,7 @@
         <v>124</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>126</v>
@@ -11502,7 +11576,7 @@
         <v>129</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>72</v>
@@ -11519,10 +11593,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11548,23 +11622,23 @@
         <v>93</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q89" s="2"/>
       <c r="R89" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="S89" t="s" s="2">
         <v>71</v>
@@ -11606,7 +11680,7 @@
         <v>71</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>72</v>
@@ -11623,10 +11697,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11649,16 +11723,16 @@
         <v>79</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11708,7 +11782,7 @@
         <v>71</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>72</v>
@@ -11725,10 +11799,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11754,16 +11828,16 @@
         <v>99</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>71</v>
@@ -11812,7 +11886,7 @@
         <v>71</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>72</v>
@@ -11829,10 +11903,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11855,19 +11929,19 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M92" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O92" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>71</v>
@@ -11916,7 +11990,7 @@
         <v>71</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>72</v>
@@ -11933,10 +12007,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11959,19 +12033,19 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>71</v>
@@ -12020,7 +12094,7 @@
         <v>71</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>72</v>
@@ -12037,13 +12111,13 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="D94" t="s" s="2">
         <v>71</v>
@@ -12065,19 +12139,19 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>195</v>
+        <v>483</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>71</v>
@@ -12102,13 +12176,13 @@
         <v>71</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>71</v>
@@ -12126,7 +12200,7 @@
         <v>71</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>72</v>
@@ -12143,10 +12217,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12169,13 +12243,13 @@
         <v>71</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12226,7 +12300,7 @@
         <v>71</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>72</v>
@@ -12243,10 +12317,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12275,7 +12349,7 @@
         <v>124</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>126</v>
@@ -12328,7 +12402,7 @@
         <v>129</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>72</v>
@@ -12345,10 +12419,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12374,23 +12448,23 @@
         <v>93</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>71</v>
@@ -12432,7 +12506,7 @@
         <v>71</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>72</v>
@@ -12449,10 +12523,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12475,16 +12549,16 @@
         <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -12534,7 +12608,7 @@
         <v>71</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>72</v>
@@ -12551,10 +12625,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12580,16 +12654,16 @@
         <v>99</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>71</v>
@@ -12638,7 +12712,7 @@
         <v>71</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>72</v>
@@ -12655,10 +12729,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12681,19 +12755,19 @@
         <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M100" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O100" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>71</v>
@@ -12742,7 +12816,7 @@
         <v>71</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>72</v>
@@ -12759,10 +12833,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12785,19 +12859,19 @@
         <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>71</v>
@@ -12846,7 +12920,7 @@
         <v>71</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>72</v>
@@ -12863,13 +12937,13 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>71</v>
@@ -12891,19 +12965,19 @@
         <v>79</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>195</v>
+        <v>497</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>71</v>
@@ -12928,13 +13002,13 @@
         <v>71</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>71</v>
@@ -12952,7 +13026,7 @@
         <v>71</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>72</v>
@@ -12969,10 +13043,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12995,13 +13069,13 @@
         <v>71</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13052,7 +13126,7 @@
         <v>71</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>72</v>
@@ -13069,10 +13143,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13101,7 +13175,7 @@
         <v>124</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>126</v>
@@ -13154,7 +13228,7 @@
         <v>129</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>72</v>
@@ -13171,10 +13245,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13200,23 +13274,23 @@
         <v>93</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>71</v>
@@ -13258,7 +13332,7 @@
         <v>71</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>72</v>
@@ -13275,10 +13349,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13301,16 +13375,16 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13360,7 +13434,7 @@
         <v>71</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>72</v>
@@ -13377,10 +13451,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13406,16 +13480,16 @@
         <v>99</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>71</v>
@@ -13464,7 +13538,7 @@
         <v>71</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>72</v>
@@ -13481,10 +13555,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13507,19 +13581,19 @@
         <v>79</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M108" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O108" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>71</v>
@@ -13568,7 +13642,7 @@
         <v>71</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>72</v>
@@ -13585,10 +13659,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13611,19 +13685,19 @@
         <v>79</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>71</v>
@@ -13672,7 +13746,7 @@
         <v>71</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>72</v>
@@ -13689,13 +13763,13 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>71</v>
@@ -13717,19 +13791,19 @@
         <v>79</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>195</v>
+        <v>511</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>71</v>
@@ -13754,13 +13828,13 @@
         <v>71</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>474</v>
+        <v>512</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>71</v>
@@ -13778,7 +13852,7 @@
         <v>71</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>72</v>
@@ -13795,10 +13869,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13821,13 +13895,13 @@
         <v>71</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -13878,7 +13952,7 @@
         <v>71</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>72</v>
@@ -13895,10 +13969,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13927,7 +14001,7 @@
         <v>124</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>126</v>
@@ -13980,7 +14054,7 @@
         <v>129</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>72</v>
@@ -13997,10 +14071,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14026,23 +14100,23 @@
         <v>93</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>71</v>
@@ -14084,7 +14158,7 @@
         <v>71</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>72</v>
@@ -14101,10 +14175,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14127,16 +14201,16 @@
         <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -14186,7 +14260,7 @@
         <v>71</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>72</v>
@@ -14203,10 +14277,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14232,16 +14306,16 @@
         <v>99</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>71</v>
@@ -14290,7 +14364,7 @@
         <v>71</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>72</v>
@@ -14307,10 +14381,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14333,19 +14407,19 @@
         <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N116" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M116" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O116" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>71</v>
@@ -14394,7 +14468,7 @@
         <v>71</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>72</v>
@@ -14411,10 +14485,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14437,19 +14511,19 @@
         <v>79</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>71</v>
@@ -14498,7 +14572,7 @@
         <v>71</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>72</v>
@@ -14515,13 +14589,13 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>71</v>
@@ -14543,19 +14617,19 @@
         <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>195</v>
+        <v>525</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>71</v>
@@ -14580,13 +14654,13 @@
         <v>71</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>474</v>
+        <v>526</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>71</v>
@@ -14604,7 +14678,7 @@
         <v>71</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>72</v>
@@ -14621,10 +14695,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14647,13 +14721,13 @@
         <v>71</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14704,7 +14778,7 @@
         <v>71</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>72</v>
@@ -14721,10 +14795,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14753,7 +14827,7 @@
         <v>124</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>126</v>
@@ -14806,7 +14880,7 @@
         <v>129</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>72</v>
@@ -14823,10 +14897,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14852,23 +14926,23 @@
         <v>93</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>71</v>
@@ -14910,7 +14984,7 @@
         <v>71</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>72</v>
@@ -14927,10 +15001,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14953,16 +15027,16 @@
         <v>79</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -15012,7 +15086,7 @@
         <v>71</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>72</v>
@@ -15029,10 +15103,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15058,16 +15132,16 @@
         <v>99</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>71</v>
@@ -15116,7 +15190,7 @@
         <v>71</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>72</v>
@@ -15133,10 +15207,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15159,19 +15233,19 @@
         <v>79</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L124" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N124" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M124" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O124" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>71</v>
@@ -15220,7 +15294,7 @@
         <v>71</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>72</v>
@@ -15237,10 +15311,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15263,19 +15337,19 @@
         <v>79</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>71</v>
@@ -15324,7 +15398,7 @@
         <v>71</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>72</v>
@@ -15341,13 +15415,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>71</v>
@@ -15369,19 +15443,19 @@
         <v>79</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>195</v>
+        <v>539</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>71</v>
@@ -15406,13 +15480,13 @@
         <v>71</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>523</v>
+        <v>448</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>71</v>
@@ -15430,7 +15504,7 @@
         <v>71</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>72</v>
@@ -15447,10 +15521,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15473,13 +15547,13 @@
         <v>71</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -15530,7 +15604,7 @@
         <v>71</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>72</v>
@@ -15547,10 +15621,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15579,7 +15653,7 @@
         <v>124</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>126</v>
@@ -15632,7 +15706,7 @@
         <v>129</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>72</v>
@@ -15649,10 +15723,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15678,23 +15752,23 @@
         <v>93</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q129" s="2"/>
       <c r="R129" t="s" s="2">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="S129" t="s" s="2">
         <v>71</v>
@@ -15736,7 +15810,7 @@
         <v>71</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>72</v>
@@ -15753,10 +15827,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15779,16 +15853,16 @@
         <v>79</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -15838,7 +15912,7 @@
         <v>71</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>72</v>
@@ -15855,10 +15929,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15884,16 +15958,16 @@
         <v>99</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>71</v>
@@ -15942,7 +16016,7 @@
         <v>71</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>72</v>
@@ -15959,10 +16033,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15985,19 +16059,19 @@
         <v>79</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L132" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M132" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O132" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>71</v>
@@ -16046,7 +16120,7 @@
         <v>71</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>72</v>
@@ -16063,10 +16137,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -16089,19 +16163,19 @@
         <v>79</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>71</v>
@@ -16150,7 +16224,7 @@
         <v>71</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>72</v>
@@ -16167,13 +16241,13 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>533</v>
+        <v>549</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>534</v>
+        <v>550</v>
       </c>
       <c r="D134" t="s" s="2">
         <v>71</v>
@@ -16195,19 +16269,19 @@
         <v>79</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>195</v>
+        <v>551</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>71</v>
@@ -16232,13 +16306,13 @@
         <v>71</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>536</v>
+        <v>552</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>71</v>
@@ -16256,7 +16330,7 @@
         <v>71</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>72</v>
@@ -16273,10 +16347,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>537</v>
+        <v>553</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16299,13 +16373,13 @@
         <v>71</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -16356,7 +16430,7 @@
         <v>71</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>72</v>
@@ -16373,10 +16447,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16405,7 +16479,7 @@
         <v>124</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>126</v>
@@ -16458,7 +16532,7 @@
         <v>129</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>72</v>
@@ -16475,10 +16549,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16504,23 +16578,23 @@
         <v>93</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>540</v>
+        <v>556</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>71</v>
@@ -16562,7 +16636,7 @@
         <v>71</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>72</v>
@@ -16579,10 +16653,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16605,16 +16679,16 @@
         <v>79</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -16664,7 +16738,7 @@
         <v>71</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>72</v>
@@ -16681,10 +16755,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>543</v>
+        <v>559</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16710,16 +16784,16 @@
         <v>99</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>71</v>
@@ -16768,7 +16842,7 @@
         <v>71</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>72</v>
@@ -16785,10 +16859,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>544</v>
+        <v>560</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16811,19 +16885,19 @@
         <v>79</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N140" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M140" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O140" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>71</v>
@@ -16872,7 +16946,7 @@
         <v>71</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>72</v>
@@ -16889,10 +16963,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>545</v>
+        <v>561</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16915,19 +16989,19 @@
         <v>79</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>71</v>
@@ -16976,7 +17050,7 @@
         <v>71</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>72</v>
@@ -16993,13 +17067,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>547</v>
+        <v>563</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>71</v>
@@ -17021,19 +17095,19 @@
         <v>79</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>195</v>
+        <v>565</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>71</v>
@@ -17058,13 +17132,13 @@
         <v>71</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>549</v>
+        <v>448</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>71</v>
@@ -17082,7 +17156,7 @@
         <v>71</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>72</v>
@@ -17099,10 +17173,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17125,13 +17199,13 @@
         <v>71</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -17182,7 +17256,7 @@
         <v>71</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>72</v>
@@ -17199,10 +17273,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17231,7 +17305,7 @@
         <v>124</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>126</v>
@@ -17284,7 +17358,7 @@
         <v>129</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>72</v>
@@ -17301,10 +17375,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17330,23 +17404,23 @@
         <v>93</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>554</v>
+        <v>570</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>71</v>
@@ -17388,7 +17462,7 @@
         <v>71</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>72</v>
@@ -17405,10 +17479,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17431,16 +17505,16 @@
         <v>79</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -17490,7 +17564,7 @@
         <v>71</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>72</v>
@@ -17507,10 +17581,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>556</v>
+        <v>572</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17536,16 +17610,16 @@
         <v>99</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>71</v>
@@ -17594,7 +17668,7 @@
         <v>71</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>72</v>
@@ -17611,10 +17685,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>557</v>
+        <v>573</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17637,19 +17711,19 @@
         <v>79</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M148" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O148" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>71</v>
@@ -17698,7 +17772,7 @@
         <v>71</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>72</v>
@@ -17715,10 +17789,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>558</v>
+        <v>574</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17741,19 +17815,19 @@
         <v>79</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>71</v>
@@ -17802,7 +17876,7 @@
         <v>71</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>72</v>
@@ -17819,13 +17893,13 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>71</v>
@@ -17847,19 +17921,19 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>195</v>
+        <v>578</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>71</v>
@@ -17884,13 +17958,13 @@
         <v>71</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>562</v>
+        <v>579</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>71</v>
@@ -17908,7 +17982,7 @@
         <v>71</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>72</v>
@@ -17925,10 +17999,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>563</v>
+        <v>580</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17951,13 +18025,13 @@
         <v>71</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -18008,7 +18082,7 @@
         <v>71</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>72</v>
@@ -18025,10 +18099,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -18057,7 +18131,7 @@
         <v>124</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>126</v>
@@ -18110,7 +18184,7 @@
         <v>129</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>72</v>
@@ -18127,10 +18201,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>565</v>
+        <v>582</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -18156,23 +18230,23 @@
         <v>93</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>567</v>
+        <v>584</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>71</v>
@@ -18214,7 +18288,7 @@
         <v>71</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>72</v>
@@ -18231,10 +18305,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -18257,16 +18331,16 @@
         <v>79</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -18316,7 +18390,7 @@
         <v>71</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>72</v>
@@ -18333,10 +18407,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -18362,16 +18436,16 @@
         <v>99</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>71</v>
@@ -18420,7 +18494,7 @@
         <v>71</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>72</v>
@@ -18437,10 +18511,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>570</v>
+        <v>587</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18463,19 +18537,19 @@
         <v>79</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N156" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M156" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O156" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>71</v>
@@ -18524,7 +18598,7 @@
         <v>71</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>72</v>
@@ -18541,10 +18615,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18567,19 +18641,19 @@
         <v>79</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>71</v>
@@ -18628,7 +18702,7 @@
         <v>71</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>72</v>
@@ -18645,13 +18719,13 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>572</v>
+        <v>589</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>71</v>
@@ -18673,19 +18747,19 @@
         <v>79</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>195</v>
+        <v>592</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>71</v>
@@ -18710,13 +18784,13 @@
         <v>71</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>71</v>
@@ -18734,7 +18808,7 @@
         <v>71</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>72</v>
@@ -18751,10 +18825,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18777,13 +18851,13 @@
         <v>71</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -18834,7 +18908,7 @@
         <v>71</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>72</v>
@@ -18851,10 +18925,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18883,7 +18957,7 @@
         <v>124</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>126</v>
@@ -18936,7 +19010,7 @@
         <v>129</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>72</v>
@@ -18953,10 +19027,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18982,23 +19056,23 @@
         <v>93</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>580</v>
+        <v>598</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>71</v>
@@ -19040,7 +19114,7 @@
         <v>71</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>72</v>
@@ -19057,10 +19131,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -19083,16 +19157,16 @@
         <v>79</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -19142,7 +19216,7 @@
         <v>71</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>72</v>
@@ -19159,10 +19233,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -19188,16 +19262,16 @@
         <v>99</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>71</v>
@@ -19246,7 +19320,7 @@
         <v>71</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>72</v>
@@ -19263,10 +19337,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -19289,19 +19363,19 @@
         <v>79</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N164" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M164" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O164" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>71</v>
@@ -19350,7 +19424,7 @@
         <v>71</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>72</v>
@@ -19367,10 +19441,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19393,19 +19467,19 @@
         <v>79</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>71</v>
@@ -19454,7 +19528,7 @@
         <v>71</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>72</v>
@@ -19471,13 +19545,13 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>585</v>
+        <v>603</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>71</v>
@@ -19499,19 +19573,19 @@
         <v>79</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>195</v>
+        <v>606</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>71</v>
@@ -19536,13 +19610,13 @@
         <v>71</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>71</v>
@@ -19560,7 +19634,7 @@
         <v>71</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>72</v>
@@ -19577,10 +19651,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>589</v>
+        <v>608</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19603,13 +19677,13 @@
         <v>71</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -19660,7 +19734,7 @@
         <v>71</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>72</v>
@@ -19677,10 +19751,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>590</v>
+        <v>609</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19709,7 +19783,7 @@
         <v>124</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N168" t="s" s="2">
         <v>126</v>
@@ -19762,7 +19836,7 @@
         <v>129</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>72</v>
@@ -19779,10 +19853,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19808,23 +19882,23 @@
         <v>93</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>71</v>
@@ -19866,7 +19940,7 @@
         <v>71</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>72</v>
@@ -19883,10 +19957,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19909,16 +19983,16 @@
         <v>79</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -19968,7 +20042,7 @@
         <v>71</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>72</v>
@@ -19985,10 +20059,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>595</v>
+        <v>614</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -20014,16 +20088,16 @@
         <v>99</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>71</v>
@@ -20072,7 +20146,7 @@
         <v>71</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>72</v>
@@ -20089,10 +20163,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -20115,19 +20189,19 @@
         <v>79</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L172" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N172" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M172" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O172" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>71</v>
@@ -20176,7 +20250,7 @@
         <v>71</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>72</v>
@@ -20193,10 +20267,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -20219,19 +20293,19 @@
         <v>79</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>71</v>
@@ -20280,7 +20354,7 @@
         <v>71</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>72</v>
@@ -20297,13 +20371,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>598</v>
+        <v>617</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>599</v>
+        <v>618</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>71</v>
@@ -20325,19 +20399,19 @@
         <v>79</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>600</v>
+        <v>619</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>195</v>
+        <v>620</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>71</v>
@@ -20362,13 +20436,13 @@
         <v>71</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>601</v>
+        <v>448</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>71</v>
@@ -20386,7 +20460,7 @@
         <v>71</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>72</v>
@@ -20403,10 +20477,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20429,13 +20503,13 @@
         <v>71</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -20486,7 +20560,7 @@
         <v>71</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>72</v>
@@ -20503,10 +20577,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20535,7 +20609,7 @@
         <v>124</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N176" t="s" s="2">
         <v>126</v>
@@ -20588,7 +20662,7 @@
         <v>129</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>72</v>
@@ -20605,10 +20679,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20634,23 +20708,23 @@
         <v>93</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>605</v>
+        <v>624</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>605</v>
+        <v>624</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>606</v>
+        <v>625</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>71</v>
@@ -20692,7 +20766,7 @@
         <v>71</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>72</v>
@@ -20709,10 +20783,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>607</v>
+        <v>626</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20735,16 +20809,16 @@
         <v>79</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -20794,7 +20868,7 @@
         <v>71</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>72</v>
@@ -20811,10 +20885,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20840,16 +20914,16 @@
         <v>99</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>71</v>
@@ -20898,7 +20972,7 @@
         <v>71</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>72</v>
@@ -20915,10 +20989,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20941,19 +21015,19 @@
         <v>79</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N180" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M180" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O180" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>71</v>
@@ -21002,7 +21076,7 @@
         <v>71</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>72</v>
@@ -21019,10 +21093,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21045,19 +21119,19 @@
         <v>79</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>71</v>
@@ -21106,7 +21180,7 @@
         <v>71</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>72</v>
@@ -21123,13 +21197,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>611</v>
+        <v>630</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>71</v>
@@ -21151,19 +21225,19 @@
         <v>79</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>613</v>
+        <v>632</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>195</v>
+        <v>633</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>71</v>
@@ -21188,13 +21262,13 @@
         <v>71</v>
       </c>
       <c r="X182" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y182" t="s" s="2">
-        <v>614</v>
+        <v>448</v>
       </c>
       <c r="Z182" t="s" s="2">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="AA182" t="s" s="2">
         <v>71</v>
@@ -21212,7 +21286,7 @@
         <v>71</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>72</v>
@@ -21229,10 +21303,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>615</v>
+        <v>634</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -21255,13 +21329,13 @@
         <v>71</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -21312,7 +21386,7 @@
         <v>71</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>72</v>
@@ -21329,10 +21403,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>616</v>
+        <v>635</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -21361,7 +21435,7 @@
         <v>124</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N184" t="s" s="2">
         <v>126</v>
@@ -21414,7 +21488,7 @@
         <v>129</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>72</v>
@@ -21431,10 +21505,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>617</v>
+        <v>636</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -21460,23 +21534,23 @@
         <v>93</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>619</v>
+        <v>638</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>71</v>
@@ -21518,7 +21592,7 @@
         <v>71</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>72</v>
@@ -21535,10 +21609,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>620</v>
+        <v>639</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21561,16 +21635,16 @@
         <v>79</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" t="s" s="2">
@@ -21620,7 +21694,7 @@
         <v>71</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>72</v>
@@ -21637,10 +21711,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>621</v>
+        <v>640</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21666,16 +21740,16 @@
         <v>99</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>71</v>
@@ -21724,7 +21798,7 @@
         <v>71</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>72</v>
@@ -21741,10 +21815,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>622</v>
+        <v>641</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21767,19 +21841,19 @@
         <v>79</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L188" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M188" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N188" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="M188" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>215</v>
-      </c>
       <c r="O188" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>71</v>
@@ -21828,7 +21902,7 @@
         <v>71</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>72</v>
@@ -21845,10 +21919,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>623</v>
+        <v>642</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21871,19 +21945,19 @@
         <v>79</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>71</v>
@@ -21932,7 +22006,7 @@
         <v>71</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>72</v>
@@ -21949,13 +22023,13 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>625</v>
+        <v>644</v>
       </c>
       <c r="D190" t="s" s="2">
         <v>71</v>
@@ -21977,19 +22051,19 @@
         <v>79</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>626</v>
+        <v>645</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>195</v>
+        <v>646</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>71</v>
@@ -22014,13 +22088,13 @@
         <v>71</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>71</v>
@@ -22038,7 +22112,7 @@
         <v>71</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>72</v>
@@ -22055,10 +22129,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -22081,19 +22155,19 @@
         <v>79</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>71</v>
@@ -22142,7 +22216,7 @@
         <v>71</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>72</v>
@@ -22159,10 +22233,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -22185,19 +22259,19 @@
         <v>71</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>632</v>
+        <v>652</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>71</v>
@@ -22246,7 +22320,7 @@
         <v>71</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>72</v>
@@ -22258,15 +22332,15 @@
         <v>90</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22289,16 +22363,16 @@
         <v>71</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -22348,7 +22422,7 @@
         <v>71</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>72</v>
@@ -22360,15 +22434,15 @@
         <v>90</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22391,13 +22465,13 @@
         <v>71</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -22448,7 +22522,7 @@
         <v>71</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>72</v>
@@ -22465,10 +22539,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22497,7 +22571,7 @@
         <v>124</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N195" t="s" s="2">
         <v>126</v>
@@ -22550,7 +22624,7 @@
         <v>129</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>72</v>
@@ -22567,10 +22641,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22593,16 +22667,16 @@
         <v>79</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -22652,7 +22726,7 @@
         <v>71</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>72</v>
@@ -22661,7 +22735,7 @@
         <v>78</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>91</v>
@@ -22669,10 +22743,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22698,13 +22772,13 @@
         <v>93</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -22730,13 +22804,13 @@
         <v>71</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>71</v>
@@ -22754,7 +22828,7 @@
         <v>71</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>72</v>
@@ -22771,10 +22845,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22797,16 +22871,16 @@
         <v>79</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -22856,7 +22930,7 @@
         <v>71</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>72</v>
@@ -22873,10 +22947,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22899,13 +22973,13 @@
         <v>71</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -22956,7 +23030,7 @@
         <v>71</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>72</v>
@@ -22973,10 +23047,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -23005,7 +23079,7 @@
         <v>124</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N200" t="s" s="2">
         <v>126</v>
@@ -23058,7 +23132,7 @@
         <v>129</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>72</v>
@@ -23075,10 +23149,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -23104,16 +23178,16 @@
         <v>99</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>71</v>
@@ -23138,13 +23212,13 @@
         <v>71</v>
       </c>
       <c r="X201" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>71</v>
@@ -23162,7 +23236,7 @@
         <v>71</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>72</v>
@@ -23179,10 +23253,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -23205,19 +23279,19 @@
         <v>79</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="O202" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>71</v>
@@ -23242,13 +23316,13 @@
         <v>71</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>71</v>
@@ -23266,7 +23340,7 @@
         <v>71</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>72</v>
@@ -23283,10 +23357,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>667</v>
+        <v>687</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>667</v>
+        <v>687</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -23312,29 +23386,29 @@
         <v>93</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q203" s="2"/>
       <c r="R203" t="s" s="2">
-        <v>671</v>
+        <v>691</v>
       </c>
       <c r="S203" t="s" s="2">
         <v>71</v>
       </c>
       <c r="T203" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="U203" t="s" s="2">
         <v>71</v>
@@ -23370,7 +23444,7 @@
         <v>71</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>72</v>
@@ -23387,10 +23461,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -23413,16 +23487,16 @@
         <v>79</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>674</v>
+        <v>694</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -23436,7 +23510,7 @@
         <v>71</v>
       </c>
       <c r="T204" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="U204" t="s" s="2">
         <v>71</v>
@@ -23472,7 +23546,7 @@
         <v>71</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>72</v>
@@ -23489,10 +23563,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>675</v>
+        <v>695</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>675</v>
+        <v>695</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -23515,16 +23589,16 @@
         <v>79</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -23574,7 +23648,7 @@
         <v>71</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>72</v>
@@ -23586,15 +23660,15 @@
         <v>90</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23617,16 +23691,16 @@
         <v>79</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -23676,7 +23750,7 @@
         <v>71</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>72</v>
@@ -23688,15 +23762,15 @@
         <v>90</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>677</v>
+        <v>697</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>677</v>
+        <v>697</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23719,16 +23793,16 @@
         <v>79</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -23778,7 +23852,7 @@
         <v>71</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>681</v>
+        <v>701</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>72</v>
@@ -23795,10 +23869,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23821,19 +23895,19 @@
         <v>71</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>683</v>
+        <v>703</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>684</v>
+        <v>704</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>685</v>
+        <v>705</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>430</v>
+        <v>706</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>71</v>
@@ -23858,11 +23932,11 @@
         <v>71</v>
       </c>
       <c r="X208" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Y208" s="2"/>
       <c r="Z208" t="s" s="2">
-        <v>687</v>
+        <v>708</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>71</v>
@@ -23880,7 +23954,7 @@
         <v>71</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>72</v>

--- a/ig/mc-changes/StructureDefinition-as-practitioner.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6792" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6792" uniqueCount="710">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T14:30:45+00:00</t>
+    <t>2023-05-09T15:20:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1723,6 +1723,9 @@
   </si>
   <si>
     <t>degreeR53</t>
+  </si>
+  <si>
+    <t>Diplôme d'un pays de l'espace économique européen.</t>
   </si>
   <si>
     <t>Synonyme MOS : DiplomeEEE</t>
@@ -16278,7 +16281,7 @@
         <v>198</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O134" t="s" s="2">
         <v>200</v>
@@ -16309,7 +16312,7 @@
         <v>179</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Z134" t="s" s="2">
         <v>449</v>
@@ -16347,7 +16350,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>451</v>
@@ -16447,7 +16450,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>453</v>
@@ -16549,7 +16552,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>455</v>
@@ -16578,7 +16581,7 @@
         <v>93</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M137" t="s" s="2">
         <v>206</v>
@@ -16594,7 +16597,7 @@
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>71</v>
@@ -16653,7 +16656,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>459</v>
@@ -16755,7 +16758,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>461</v>
@@ -16859,7 +16862,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>463</v>
@@ -16963,7 +16966,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>465</v>
@@ -17067,13 +17070,13 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>442</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D142" t="s" s="2">
         <v>71</v>
@@ -17098,13 +17101,13 @@
         <v>196</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M142" t="s" s="2">
         <v>198</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O142" t="s" s="2">
         <v>200</v>
@@ -17173,7 +17176,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>451</v>
@@ -17273,7 +17276,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>453</v>
@@ -17375,7 +17378,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>455</v>
@@ -17404,10 +17407,10 @@
         <v>93</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N145" t="s" s="2">
         <v>207</v>
@@ -17420,7 +17423,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>71</v>
@@ -17479,7 +17482,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>459</v>
@@ -17581,7 +17584,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>461</v>
@@ -17685,7 +17688,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>463</v>
@@ -17789,7 +17792,7 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>465</v>
@@ -17893,13 +17896,13 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>442</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D150" t="s" s="2">
         <v>71</v>
@@ -17924,13 +17927,13 @@
         <v>196</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M150" t="s" s="2">
         <v>198</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O150" t="s" s="2">
         <v>200</v>
@@ -17961,7 +17964,7 @@
         <v>179</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z150" t="s" s="2">
         <v>449</v>
@@ -17999,7 +18002,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>451</v>
@@ -18099,7 +18102,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>453</v>
@@ -18201,7 +18204,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>455</v>
@@ -18230,10 +18233,10 @@
         <v>93</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N153" t="s" s="2">
         <v>207</v>
@@ -18246,7 +18249,7 @@
       </c>
       <c r="Q153" s="2"/>
       <c r="R153" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S153" t="s" s="2">
         <v>71</v>
@@ -18305,7 +18308,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>459</v>
@@ -18407,7 +18410,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>461</v>
@@ -18511,7 +18514,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>463</v>
@@ -18615,7 +18618,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>465</v>
@@ -18719,13 +18722,13 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>442</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D158" t="s" s="2">
         <v>71</v>
@@ -18750,13 +18753,13 @@
         <v>196</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M158" t="s" s="2">
         <v>198</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O158" t="s" s="2">
         <v>200</v>
@@ -18787,7 +18790,7 @@
         <v>179</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Z158" t="s" s="2">
         <v>449</v>
@@ -18825,7 +18828,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>451</v>
@@ -18925,7 +18928,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>453</v>
@@ -19027,7 +19030,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>455</v>
@@ -19056,7 +19059,7 @@
         <v>93</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M161" t="s" s="2">
         <v>206</v>
@@ -19072,7 +19075,7 @@
       </c>
       <c r="Q161" s="2"/>
       <c r="R161" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>71</v>
@@ -19131,7 +19134,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>459</v>
@@ -19233,7 +19236,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>461</v>
@@ -19337,7 +19340,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>463</v>
@@ -19441,7 +19444,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>465</v>
@@ -19545,13 +19548,13 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>442</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D166" t="s" s="2">
         <v>71</v>
@@ -19576,13 +19579,13 @@
         <v>196</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M166" t="s" s="2">
         <v>198</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="O166" t="s" s="2">
         <v>200</v>
@@ -19613,7 +19616,7 @@
         <v>179</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Z166" t="s" s="2">
         <v>449</v>
@@ -19651,7 +19654,7 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>451</v>
@@ -19751,7 +19754,7 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>453</v>
@@ -19853,7 +19856,7 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>455</v>
@@ -19882,10 +19885,10 @@
         <v>93</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>207</v>
@@ -19898,7 +19901,7 @@
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>71</v>
@@ -19957,7 +19960,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>459</v>
@@ -20059,7 +20062,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>461</v>
@@ -20163,7 +20166,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>463</v>
@@ -20267,7 +20270,7 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>465</v>
@@ -20371,13 +20374,13 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>442</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>71</v>
@@ -20402,13 +20405,13 @@
         <v>196</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M174" t="s" s="2">
         <v>198</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O174" t="s" s="2">
         <v>200</v>
@@ -20477,7 +20480,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>451</v>
@@ -20577,7 +20580,7 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>453</v>
@@ -20679,7 +20682,7 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B177" t="s" s="2">
         <v>455</v>
@@ -20708,10 +20711,10 @@
         <v>93</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N177" t="s" s="2">
         <v>207</v>
@@ -20724,7 +20727,7 @@
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>71</v>
@@ -20783,7 +20786,7 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>459</v>
@@ -20885,7 +20888,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>461</v>
@@ -20989,7 +20992,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>463</v>
@@ -21093,7 +21096,7 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>465</v>
@@ -21197,13 +21200,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>442</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>71</v>
@@ -21228,13 +21231,13 @@
         <v>196</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M182" t="s" s="2">
         <v>198</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O182" t="s" s="2">
         <v>200</v>
@@ -21303,7 +21306,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>451</v>
@@ -21403,7 +21406,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>453</v>
@@ -21505,7 +21508,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>455</v>
@@ -21534,7 +21537,7 @@
         <v>93</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M185" t="s" s="2">
         <v>206</v>
@@ -21550,7 +21553,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>71</v>
@@ -21609,7 +21612,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>459</v>
@@ -21711,7 +21714,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>461</v>
@@ -21815,7 +21818,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>463</v>
@@ -21919,7 +21922,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>465</v>
@@ -22023,13 +22026,13 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>442</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D190" t="s" s="2">
         <v>71</v>
@@ -22054,13 +22057,13 @@
         <v>196</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M190" t="s" s="2">
         <v>198</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O190" t="s" s="2">
         <v>200</v>
@@ -22091,10 +22094,10 @@
         <v>179</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>71</v>
@@ -22129,10 +22132,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -22233,10 +22236,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -22262,16 +22265,16 @@
         <v>254</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N192" t="s" s="2">
         <v>257</v>
       </c>
       <c r="O192" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>71</v>
@@ -22320,7 +22323,7 @@
         <v>71</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>72</v>
@@ -22337,10 +22340,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -22366,13 +22369,13 @@
         <v>261</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="O193" s="2"/>
       <c r="P193" t="s" s="2">
@@ -22422,7 +22425,7 @@
         <v>71</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>72</v>
@@ -22439,10 +22442,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -22539,10 +22542,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22641,10 +22644,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22670,13 +22673,13 @@
         <v>167</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
@@ -22726,7 +22729,7 @@
         <v>71</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>72</v>
@@ -22735,7 +22738,7 @@
         <v>78</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>91</v>
@@ -22743,10 +22746,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22772,13 +22775,13 @@
         <v>93</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
@@ -22807,10 +22810,10 @@
         <v>189</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>71</v>
@@ -22828,7 +22831,7 @@
         <v>71</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>72</v>
@@ -22845,10 +22848,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22874,13 +22877,13 @@
         <v>162</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -22930,7 +22933,7 @@
         <v>71</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>72</v>
@@ -22947,10 +22950,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -23047,10 +23050,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -23149,10 +23152,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -23218,7 +23221,7 @@
         <v>180</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>71</v>
@@ -23253,10 +23256,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -23282,13 +23285,13 @@
         <v>184</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="M202" t="s" s="2">
         <v>186</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="O202" t="s" s="2">
         <v>188</v>
@@ -23319,10 +23322,10 @@
         <v>189</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>71</v>
@@ -23357,10 +23360,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -23386,13 +23389,13 @@
         <v>93</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O203" t="s" s="2">
         <v>244</v>
@@ -23402,7 +23405,7 @@
       </c>
       <c r="Q203" s="2"/>
       <c r="R203" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="S203" t="s" s="2">
         <v>71</v>
@@ -23461,10 +23464,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -23490,13 +23493,13 @@
         <v>167</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M204" t="s" s="2">
         <v>249</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -23563,10 +23566,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -23665,10 +23668,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23767,10 +23770,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23796,13 +23799,13 @@
         <v>167</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -23852,7 +23855,7 @@
         <v>71</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>72</v>
@@ -23869,10 +23872,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23895,19 +23898,19 @@
         <v>71</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>71</v>
@@ -23936,7 +23939,7 @@
       </c>
       <c r="Y208" s="2"/>
       <c r="Z208" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="AA208" t="s" s="2">
         <v>71</v>
@@ -23954,7 +23957,7 @@
         <v>71</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>72</v>

--- a/ig/mc-changes/StructureDefinition-as-practitioner.xlsx
+++ b/ig/mc-changes/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T16:25:19+00:00</t>
+    <t>2023-05-16T15:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
